--- a/puntos_extra.xlsx
+++ b/puntos_extra.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="15">
   <si>
     <t xml:space="preserve">G</t>
   </si>
@@ -46,6 +46,9 @@
     <t xml:space="preserve">HQ</t>
   </si>
   <si>
+    <t xml:space="preserve">NO ES GRAY CODE</t>
+  </si>
+  <si>
     <t xml:space="preserve">0 . 0</t>
   </si>
   <si>
@@ -56,6 +59,12 @@
   </si>
   <si>
     <t xml:space="preserve">1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.</t>
   </si>
 </sst>
 </file>
@@ -70,6 +79,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -129,8 +139,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -257,216 +271,296 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="E9:O29"/>
+  <dimension ref="E9:O33"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E9" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="F9" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="G9" s="0" t="s">
+      <c r="E9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J9" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="K9" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="L9" s="0" t="s">
+      <c r="J9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M9" s="0" t="s">
+      <c r="M9" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="0" t="n">
+      <c r="E10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" s="0" t="n">
+      <c r="E11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E12" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="0" t="s">
+      <c r="E12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" s="0" t="n">
+      <c r="J12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E13" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="0" t="s">
+      <c r="E13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="0" t="n">
+      <c r="J13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J14" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="0" t="n">
+      <c r="J14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J15" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" s="0" t="n">
+      <c r="J15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J16" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" s="0" t="n">
+      <c r="J16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J17" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="0" t="n">
+      <c r="J17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J22" s="0" t="s">
+      <c r="J22" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L24" s="0" t="s">
+      <c r="L24" s="1" t="s">
         <v>7</v>
       </c>
     </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M25" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L26" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="M26" s="0" t="s">
+      <c r="J26" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="L26" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="N26" s="0" t="s">
+      <c r="M26" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="O26" s="0" t="s">
+      <c r="N26" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="O26" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K27" s="0" t="n">
+      <c r="K27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K28" s="0" t="n">
+      <c r="K28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J29" s="0" t="s">
+      <c r="J29" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L31" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="M31" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="N31" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="O31" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K33" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="O33" s="0" t="n">
         <v>0</v>
       </c>
     </row>

--- a/puntos_extra.xlsx
+++ b/puntos_extra.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
   <si>
     <t xml:space="preserve">G</t>
   </si>
@@ -65,6 +65,9 @@
   </si>
   <si>
     <t xml:space="preserve">1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">un grupo es  &lt;not g&gt; and &lt;not h&gt;   otro es  &lt;not H &gt;and&lt; not q&gt;  el ultimo es  g and h and q</t>
   </si>
 </sst>
 </file>
@@ -271,7 +274,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="E9:O33"/>
+  <dimension ref="E9:Q33"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -456,12 +459,12 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M25" s="0" t="s">
+      <c r="M25" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J26" s="0" t="s">
+      <c r="J26" s="1" t="s">
         <v>0</v>
       </c>
       <c r="L26" s="1" t="s">
@@ -481,16 +484,16 @@
       <c r="K27" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="L27" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="0" t="n">
+      <c r="L27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -498,16 +501,16 @@
       <c r="K28" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L28" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M28" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="0" t="n">
+      <c r="L28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -517,51 +520,54 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L31" s="0" t="s">
+      <c r="L31" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M31" s="0" t="s">
+      <c r="M31" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="N31" s="0" t="s">
+      <c r="N31" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O31" s="0" t="s">
+      <c r="O31" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K32" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M32" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="N32" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="0" t="n">
+      <c r="K32" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K33" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M33" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="0" t="s">
+      <c r="K33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="O33" s="0" t="n">
-        <v>0</v>
+      <c r="O33" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="0" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -569,8 +575,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Página &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Página &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/puntos_extra.xlsx
+++ b/puntos_extra.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="17">
   <si>
     <t xml:space="preserve">G</t>
   </si>
@@ -68,6 +68,9 @@
   </si>
   <si>
     <t xml:space="preserve">un grupo es  &lt;not g&gt; and &lt;not h&gt;   otro es  &lt;not H &gt;and&lt; not q&gt;  el ultimo es  g and h and q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q_next = ~G~H + ~H~q + Ghq</t>
   </si>
 </sst>
 </file>
@@ -77,7 +80,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -98,6 +101,11 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Courier New"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -142,12 +150,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -274,7 +290,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="E9:Q33"/>
+  <dimension ref="E9:Q35"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -520,6 +536,7 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K31" s="2"/>
       <c r="L31" s="1" t="s">
         <v>13</v>
       </c>
@@ -566,8 +583,13 @@
       <c r="O33" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" s="0" t="s">
+      <c r="Q33" s="1" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K35" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -575,8 +597,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Página &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Página &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>